--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8446-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8446-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC6AB75F-8369-4333-A5AD-5C1142E379A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C90A5193-C361-4CD6-817A-5FE032BF5D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6B3E0DBB-CA5A-47A8-AACF-F8113CA08FC6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E9B1AA8E-92D5-44D2-8928-D17DCC2BC9FE}"/>
   </bookViews>
   <sheets>
     <sheet name="8446-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1499,19 +1499,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48803EA9-0299-4E47-849A-E07BCF377456}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E216AF-F682-4DD2-BC3A-F215B00F3834}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1665,7 +1665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2019</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2018</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2017</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2016</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2015</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2014</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2013</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
         <v>52</v>
       </c>
